--- a/review-tasks/1c-load-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1c-load-review/jury/scoring-sheet.xlsx
@@ -438,7 +438,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="45" customWidth="1" min="5" max="5"/>
     <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -474,7 +474,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>0 или 1</t>
+          <t>Найден (1/0)</t>
         </is>
       </c>
     </row>
@@ -3694,7 +3694,12 @@
       </c>
       <c r="F103" s="3" t="inlineStr">
         <is>
-          <t>Ставим 1, если участник предлагает «исправить» это место. Если сам объяснил, почему место верно, — 0. Каждая ловушка −2 балла</t>
+          <t>Ставим 1, если участник считает это место ошибкой. Если сам объяснил, почему место верно, — 0. Каждая ловушка −2 балла</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>Попался (1/0)</t>
         </is>
       </c>
     </row>
